--- a/staged_data/vyhodnotenie_VS/vyhodnotenie_VS.xlsx
+++ b/staged_data/vyhodnotenie_VS/vyhodnotenie_VS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TIBOR\work\projektovanie\zakazky\py\pyproj\gtm\output_test_structured_TEMPORARY\vyhodnotenie_VS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TIBOR\work\projektovanie\zakazky\py\pyproj\gtm\output_test_structured\vyhodnotenie_VS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9747C1-D445-4BEE-9C4A-C4B0F9A95980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB349B2-F2FA-428A-B4CD-259986C33E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Vyhodnotenie" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Vyhodnotenie!$A$1:$J$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Vyhodnotenie!$A$1:$J$224</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="578">
   <si>
     <t>inkl.</t>
   </si>
@@ -637,12 +637,6 @@
     <t>19.6</t>
   </si>
   <si>
-    <t>8.0</t>
-  </si>
-  <si>
-    <t>244.9 %</t>
-  </si>
-  <si>
     <t>235.0</t>
   </si>
   <si>
@@ -652,12 +646,6 @@
     <t>37.8 %</t>
   </si>
   <si>
-    <t>η = 244.9 %</t>
-  </si>
-  <si>
-    <t>Havarijný stav</t>
-  </si>
-  <si>
     <t>IVS-104</t>
   </si>
   <si>
@@ -760,39 +748,21 @@
     <t>159.7</t>
   </si>
   <si>
-    <t>43.7</t>
-  </si>
-  <si>
-    <t>365.5 %</t>
-  </si>
-  <si>
     <t>980.0</t>
   </si>
   <si>
     <t>1073.1</t>
   </si>
   <si>
-    <t>47.1 %</t>
-  </si>
-  <si>
-    <t>η = 365.5 %</t>
-  </si>
-  <si>
     <t>IVS-110</t>
   </si>
   <si>
     <t>94.8</t>
   </si>
   <si>
-    <t>216.9 %</t>
-  </si>
-  <si>
     <t>745.0</t>
   </si>
   <si>
-    <t>η = 216.9 %</t>
-  </si>
-  <si>
     <t>IVS-111</t>
   </si>
   <si>
@@ -1372,23 +1342,428 @@
     <t>16.04.2024</t>
   </si>
   <si>
-    <t>26.4</t>
-  </si>
-  <si>
-    <t>12.0</t>
-  </si>
-  <si>
-    <t>220.4 %</t>
-  </si>
-  <si>
-    <t>η = 220.4 %</t>
+    <t>17_INK-1</t>
+  </si>
+  <si>
+    <t>Limitná hodnota nebola definovaná</t>
+  </si>
+  <si>
+    <t>23_INK-1</t>
+  </si>
+  <si>
+    <t>23_INK-3</t>
+  </si>
+  <si>
+    <t>24_INK-1</t>
+  </si>
+  <si>
+    <t>24_INK-2</t>
+  </si>
+  <si>
+    <t>25_INK-2</t>
+  </si>
+  <si>
+    <t>25_INK-4</t>
+  </si>
+  <si>
+    <t>27_INK-2</t>
+  </si>
+  <si>
+    <t>IGP-Z-1</t>
+  </si>
+  <si>
+    <t>IGP-Z-5</t>
+  </si>
+  <si>
+    <t>IGP-Z-6</t>
+  </si>
+  <si>
+    <t>INK-237-4</t>
+  </si>
+  <si>
+    <t>INK-LA-100</t>
+  </si>
+  <si>
+    <t>INK-LB-100</t>
+  </si>
+  <si>
+    <t>INK-LB-101</t>
+  </si>
+  <si>
+    <t>INK-LB-102</t>
+  </si>
+  <si>
+    <t>INK-LB-103</t>
+  </si>
+  <si>
+    <t>IVS-102</t>
+  </si>
+  <si>
+    <t>IGP-Z-3</t>
+  </si>
+  <si>
+    <t>IGP-Z-4</t>
+  </si>
+  <si>
+    <t>IV-43</t>
+  </si>
+  <si>
+    <t>IV-46</t>
+  </si>
+  <si>
+    <t>IV-48</t>
+  </si>
+  <si>
+    <t>IV-57</t>
+  </si>
+  <si>
+    <t>IV-70</t>
+  </si>
+  <si>
+    <t>IV-72</t>
+  </si>
+  <si>
+    <t>IV-75</t>
+  </si>
+  <si>
+    <t>IV-78</t>
+  </si>
+  <si>
+    <t>IV-82</t>
+  </si>
+  <si>
+    <t>JIN-2</t>
+  </si>
+  <si>
+    <t>13a_INK-1</t>
+  </si>
+  <si>
+    <t>13a_INK-2</t>
+  </si>
+  <si>
+    <t>13b_INK-1</t>
+  </si>
+  <si>
+    <t>13b_INK-2</t>
+  </si>
+  <si>
+    <t>13c_INK-1</t>
+  </si>
+  <si>
+    <t>13c_INK-2</t>
+  </si>
+  <si>
+    <t>15_INK-2</t>
+  </si>
+  <si>
+    <t>15_INK3</t>
+  </si>
+  <si>
+    <t>16_INK-1</t>
+  </si>
+  <si>
+    <t>20_INK-1</t>
+  </si>
+  <si>
+    <t>21_INK-1</t>
+  </si>
+  <si>
+    <t>23_INK-2</t>
+  </si>
+  <si>
+    <t>25_INK-1</t>
+  </si>
+  <si>
+    <t>26_INK-1</t>
+  </si>
+  <si>
+    <t>DIV-1</t>
+  </si>
+  <si>
+    <t>DIV-2</t>
+  </si>
+  <si>
+    <t>DIV-3</t>
+  </si>
+  <si>
+    <t>I-VP-1</t>
+  </si>
+  <si>
+    <t>I-VP-3</t>
+  </si>
+  <si>
+    <t>IV-04</t>
+  </si>
+  <si>
+    <t>IV-06</t>
+  </si>
+  <si>
+    <t>IV-12</t>
+  </si>
+  <si>
+    <t>IV-14</t>
+  </si>
+  <si>
+    <t>IV-15</t>
+  </si>
+  <si>
+    <t>IV-16</t>
+  </si>
+  <si>
+    <t>IV-1</t>
+  </si>
+  <si>
+    <t>IV-20</t>
+  </si>
+  <si>
+    <t>IV-21</t>
+  </si>
+  <si>
+    <t>IV-22</t>
+  </si>
+  <si>
+    <t>IV-232-45-2</t>
+  </si>
+  <si>
+    <t>IV-232-50-1</t>
+  </si>
+  <si>
+    <t>IV-233-45-3</t>
+  </si>
+  <si>
+    <t>IV-23</t>
+  </si>
+  <si>
+    <t>IV-24</t>
+  </si>
+  <si>
+    <t>IV-27</t>
+  </si>
+  <si>
+    <t>IV-28</t>
+  </si>
+  <si>
+    <t>IV-2</t>
+  </si>
+  <si>
+    <t>IV-30</t>
+  </si>
+  <si>
+    <t>IV-31</t>
+  </si>
+  <si>
+    <t>IV-33</t>
+  </si>
+  <si>
+    <t>IV-36</t>
+  </si>
+  <si>
+    <t>IV-37</t>
+  </si>
+  <si>
+    <t>IV-39</t>
+  </si>
+  <si>
+    <t>IV-40</t>
+  </si>
+  <si>
+    <t>IV-42</t>
+  </si>
+  <si>
+    <t>IV-44</t>
+  </si>
+  <si>
+    <t>IV-47</t>
+  </si>
+  <si>
+    <t>IV-49</t>
+  </si>
+  <si>
+    <t>IV-50</t>
+  </si>
+  <si>
+    <t>IV-55</t>
+  </si>
+  <si>
+    <t>IV-56</t>
+  </si>
+  <si>
+    <t>IV-58</t>
+  </si>
+  <si>
+    <t>IV-61</t>
+  </si>
+  <si>
+    <t>IV-62</t>
+  </si>
+  <si>
+    <t>IV-63</t>
+  </si>
+  <si>
+    <t>IV-64</t>
+  </si>
+  <si>
+    <t>IV-65</t>
+  </si>
+  <si>
+    <t>IV-66</t>
+  </si>
+  <si>
+    <t>IV-67</t>
+  </si>
+  <si>
+    <t>IV-68</t>
+  </si>
+  <si>
+    <t>IV-71</t>
+  </si>
+  <si>
+    <t>IV-76</t>
+  </si>
+  <si>
+    <t>IV-77</t>
+  </si>
+  <si>
+    <t>IV-79</t>
+  </si>
+  <si>
+    <t>IV-80</t>
+  </si>
+  <si>
+    <t>IV-81</t>
+  </si>
+  <si>
+    <t>IV-83</t>
+  </si>
+  <si>
+    <t>IV-S73</t>
+  </si>
+  <si>
+    <t>IVS-101</t>
+  </si>
+  <si>
+    <t>JIN-1</t>
+  </si>
+  <si>
+    <t>JIN-3</t>
+  </si>
+  <si>
+    <t>JIN-4</t>
+  </si>
+  <si>
+    <t>JIN-5</t>
+  </si>
+  <si>
+    <t>JIND-07</t>
+  </si>
+  <si>
+    <t>JIND-6</t>
+  </si>
+  <si>
+    <t>JIND-8</t>
+  </si>
+  <si>
+    <t>NT-02</t>
+  </si>
+  <si>
+    <t>NT-04</t>
+  </si>
+  <si>
+    <t>NT-06</t>
+  </si>
+  <si>
+    <t>NT-07</t>
+  </si>
+  <si>
+    <t>NT-09</t>
+  </si>
+  <si>
+    <t>NT-19</t>
+  </si>
+  <si>
+    <t>NT-20</t>
+  </si>
+  <si>
+    <t>NT-25</t>
+  </si>
+  <si>
+    <t>NT-26</t>
+  </si>
+  <si>
+    <t>12_INK-1</t>
+  </si>
+  <si>
+    <t>INK-LB-104</t>
+  </si>
+  <si>
+    <t>INK-LB-105</t>
+  </si>
+  <si>
+    <t>INK-LB-106</t>
+  </si>
+  <si>
+    <t>INK-LB-107</t>
+  </si>
+  <si>
+    <t>INK-LB-103N</t>
+  </si>
+  <si>
+    <t>INK-LB-104N</t>
+  </si>
+  <si>
+    <t>IV-66N</t>
+  </si>
+  <si>
+    <t>INK-214-1</t>
+  </si>
+  <si>
+    <t>25.6</t>
+  </si>
+  <si>
+    <t>102.6 %</t>
+  </si>
+  <si>
+    <t>η = 102.6 %</t>
+  </si>
+  <si>
+    <t>228.0</t>
+  </si>
+  <si>
+    <t>70.1 %</t>
+  </si>
+  <si>
+    <t>91.3 %</t>
+  </si>
+  <si>
+    <t>η = 91.3 %</t>
+  </si>
+  <si>
+    <t>154.0</t>
+  </si>
+  <si>
+    <t>73.4 %</t>
+  </si>
+  <si>
+    <t>69.4 %</t>
+  </si>
+  <si>
+    <t>η = 73.4 %</t>
+  </si>
+  <si>
+    <t>16.65</t>
+  </si>
+  <si>
+    <t>7.2 %</t>
+  </si>
+  <si>
+    <t>η = 7.2 %</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1398,21 +1773,36 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="calibri"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="calibri"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1436,7 +1826,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB22222"/>
+        <fgColor rgb="FFF79646"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90EE90"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0E68C"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1467,28 +1870,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1792,3219 +2202,4212 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J224"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="36" customWidth="1"/>
+    <col min="1" max="1" width="10" style="3" customWidth="1"/>
+    <col min="2" max="5" width="20" style="3" customWidth="1"/>
+    <col min="6" max="6" width="28" style="3" customWidth="1"/>
+    <col min="7" max="8" width="20" style="3" customWidth="1"/>
+    <col min="9" max="9" width="22" style="3" customWidth="1"/>
+    <col min="10" max="10" width="36" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="J20" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="H22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="J24" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H26" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="J28" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J29" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H30" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="I30" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J30" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="J31" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="J32" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I33" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J33" s="6" t="s">
+      <c r="J33" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H34" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J34" s="6" t="s">
+      <c r="J34" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J35" s="6" t="s">
+      <c r="J35" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="H36" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="J37" s="6" t="s">
+      <c r="J37" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I38" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="J38" s="6" t="s">
+      <c r="J38" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="J39" s="5" t="s">
+      <c r="J39" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H40" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="J40" s="6" t="s">
+      <c r="J40" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="J41" s="5" t="s">
+      <c r="J41" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="G42" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="H42" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="I42" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="B43" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="D43" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="J42" s="7" t="s">
+      <c r="E43" s="1" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="F43" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="G43" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F43" s="3" t="s">
+      <c r="C44" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="H43" s="3" t="s">
+      <c r="D44" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="E44" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J43" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="F44" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="G44" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C45" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="H45" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="J70" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="J88" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="J92" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H94" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="I44" s="3" t="s">
+      <c r="I94" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="J44" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F47" s="3" t="s">
+      <c r="G95" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H49" s="3" t="s">
+      <c r="C97" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="J97" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="J98" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H100" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="J53" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="J55" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="J58" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="J59" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="J61" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J62" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J63" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="J64" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="J65" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="J66" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="J67" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="J68" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="J69" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="J70" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="J71" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="J72" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="J73" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="J74" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="J75" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="J76" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="J77" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J78" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J79" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="J80" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="J81" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="J83" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="J84" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J85" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="J86" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="J87" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="J88" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="J89" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="J91" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="J92" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="J93" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="J94" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="J95" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="J96" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="H97" s="3" t="s">
+      <c r="I100" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="J100" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="I97" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="J97" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
+      <c r="J101" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="E98" s="3" t="s">
+      <c r="J102" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="J103" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="G98" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="H98" s="3" t="s">
+      <c r="J104" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="I98" s="3" t="s">
+      <c r="J105" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="J98" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
+      <c r="J106" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
+      <c r="J107" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="J108" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="J109" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="J110" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="J111" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I100" s="3" t="s">
+      <c r="J112" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="J100" s="7" t="s">
-        <v>210</v>
+      <c r="J113" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="J117" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="J119" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J121" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="J123" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="J128" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="J129" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="J130" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="J131" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="J132" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="J133" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="J134" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="J135" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="J136" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="J142" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="J143" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="J144" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="J147" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="J148" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="J149" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="J150" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="J151" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="J152" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="J153" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="J154" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="J155" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="J156" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="J157" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="J158" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="J159" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="J160" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="J161" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="J162" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="J163" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="J164" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="J165" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="J166" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="J167" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="J168" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="J169" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="J170" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="J171" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="J172" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="J173" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="J174" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="J175" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="J176" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="J177" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="J178" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="J179" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="J180" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="J181" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="J182" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="J183" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="J184" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="J185" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="J186" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="J187" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="J188" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="J189" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="J190" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="J191" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="J192" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="J193" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="J194" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="J195" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="J196" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="J197" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="J198" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="J199" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="J200" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="J201" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="J202" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="J203" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="J204" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="J205" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="J206" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="J207" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="J208" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="J209" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="J210" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="J211" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="J212" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="J213" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="J214" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A215" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="J215" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A216" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="J216" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A217" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="J217" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A218" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="J218" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A219" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="J219" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A220" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="J220" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A221" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="J221" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A222" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="J222" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A223" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="J223" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A224" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="J224" s="3" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J100" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J224" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>